--- a/Result/checksun_type/電力系統.xlsx
+++ b/Result/checksun_type/電力系統.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>919.4</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>948.95</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>947.82</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>948.95</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>947.8200000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>10702402903.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>13777681330.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>13777681330.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>13184190874.5</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>14165986897.28</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>14165986897.28</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-288049536.2624874</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>10702402903</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>10702402903.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>909.2</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>954.7</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>945.54</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>954.7</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>945.54</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>9579043601.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>13831910429.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>13831910429.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>13509805904.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>14413977761.06</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>14413977761.06</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-94238805.57345963</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>9579043601</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>9579043601.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>906.8</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>962.95</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>944.08</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>962.95</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>944.08</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>16911194399.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>14386844246.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>14386844246.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>13675683609.2</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>14618581897.64</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>14618581897.64</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>306359263.681345</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>16911194399</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>16911194399.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>911.4</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>971.8</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>941.9</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>971.8</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>941.9</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>15812987742.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>13146559354.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>13146559354.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>13118876980.5</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>14614553602.28</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>14614553602.28</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>82113231.98530579</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>15812987742</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>15812987742.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>916.8</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>977.55</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>938.52</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>977.55</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>938.52</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>15882778006.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>13620510362.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>13620510362.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>12470961715.4</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>14466055493.78</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>14466055493.78</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-123505858.3299389</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>15882778006</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>15882778006.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>917.6</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>980.85</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>933.96</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>980.85</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>933.96</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>10973548400.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>12590700418.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>12590700418.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>11918833012.0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>14368721493.28</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>14368721493.28</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-420314020.6970749</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>10973548400</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>10973548400.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>932.2</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>987.15</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>929.9</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>987.15</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>929.9</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>12353712685.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>13187701378.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>13187701378.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>12539817288.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>14292572173.18</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>14292572173.18</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-303325579.8395176</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>12353712685</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>12353712685.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>947.0</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>993.0</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>925.54</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>993</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>925.54</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>10709769939.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>12964522972.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>12964522972</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>13184192924.4</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>14209168625.62</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>14209168625.62</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-273240924.15588</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>10709769939</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>10709769939.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>960.2</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>997.15</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>920.92</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>997.15</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>920.92</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>18182742782.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>13091194606.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>13091194606.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>13748861147.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>14155319682.02</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>14155319682.02</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-44367517.38797188</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>18182742782</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>18182742782.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>968.8</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>1002.3</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>916.24</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>1002.3</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>916.24</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>10733728288.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>11321413068.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>11321413068.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>14033372540.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>13994353884.38</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>13994353884.38</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-516496615.2771072</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>10733728288</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>10733728288.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>972.8</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>1005.15</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>911.3</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>1005.15</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>911.3</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>13958553198.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>11246965605.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>11246965605.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>15377407355.7</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>13940555876.02</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>13940555876.02</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-374411751.6445465</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>13958553198</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>13958553198.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>701.8</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>734.15</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>644.12</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>734.15</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>644.12</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>2145406818.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>4705713538.6</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>4705713538.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>2697328683.0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>2381458909.08</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>2381458909.08</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>47833880.16900253</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>2145406818</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2145406818.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>712.8</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>729.6</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>642.32</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>729.6</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>642.3200000000001</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>2917531202.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>4446393537.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>4446393537.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>2537135784.1</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>2394527724.36</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>2394527724.36</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>171300840.0050039</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>2917531202</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2917531202.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>718.0</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>726.45</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>641.18</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>726.45</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>641.1799999999999</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>3308931687.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>3977678243.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>3977678243.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>2336901368.1</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>2356977274.04</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>2356977274.04</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>258836711.484827</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>3308931687</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>3308931687.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>724.4</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>720.75</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>639.48</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>720.75</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>639.48</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>9396894111.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>3406595539.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>3406595539.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>2092972596.2</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>2319670873.56</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>2319670873.56</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>332708021.9386873</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>9396894111</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>9396894111.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>731.2</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>715.55</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>638.3</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>715.55</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>638.3</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>5759803875.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>1689450518.2</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>1689450518.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>1272693479.4</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>2149905312.46</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>2149905312.46</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-225925652.1964645</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>5759803875</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>5759803875.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>732.4</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>708.6</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>635.96</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>708.6</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>635.96</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>848806811.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>688943827.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>688943827.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>860708905.5</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>2069337538.82</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>2069337538.82</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-626216745.2396646</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>848806811</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>848806811.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>735.4</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>701.1</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>633.54</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>701.1</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>633.54</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>573954733.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>627878031.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>627878031</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>1516353585.7</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>2106062606.14</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>2106062606.14</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-649518023.2571056</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>573954733</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>573954733.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>745.6</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>695.2</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>631.48</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>695.2</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>631.48</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>453518166.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>696124492.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>696124492.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>2883970531.7</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>2126707687.18</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>2126707687.18</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-630160054.0942674</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>453518166</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>453518166.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>752.0</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>688.05</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>628.72</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>688.05</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>628.72</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>811169006.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>779349653.2</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>779349653.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>4079717323.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>2168937186.34</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>2168937186.34</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-567096178.3225608</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>811169006</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>811169006.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>756.8</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>681.7</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>626.7</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>681.7</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>626.7</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>757270421.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>855936440.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>855936440.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>4864530439.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>2227082877.5</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>2227082877.5</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-495071225.1371737</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>757270421</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>757270421.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>760.8</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>673.0</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>624.74</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>673</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>624.74</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>543477829.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>1032473983.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>1032473983.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>5522062366.6</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>2292721646.52</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>2292721646.52</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-368722471.2960072</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>543477829</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>543477829.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>96.16</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>102.5</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>101.88</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>101.88</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>159843579.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>323909709.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>323909709.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>303527778.0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>427891465.06</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>427891465.06</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-91694911.4967857</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>159843579</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>159843579.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>95.75999999999999</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>102.53</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>102.08</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>102.53</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>102.08</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>145859250.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>348234730.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>348234730.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>311622176.9</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>429640696.94</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>429640696.94</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-86779351.10592324</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>145859250</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>145859250.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>96.12</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>102.68</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>102.33</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>102.68</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>102.33</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>182336206.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>376915742.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>376915742.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>322711393.4</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>429470961.98</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>429470961.98</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-75159538.47233671</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>182336206</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>182336206.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>96.56</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>102.82</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>102.56</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>102.82</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>102.56</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>714004012.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>384535008.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>384535008.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>335344540.6</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>431976435.3</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>431976435.3</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-59783782.19320107</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>714004012</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>714004012.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>97.24000000000001</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>103.04</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>102.79</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>103.04</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>102.79</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>417505501.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>313755822.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>313755822.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>306400241.3</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>420660383.62</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>420660383.62</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-92647688.78753585</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>417505501</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>417505501.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>97.82</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>103.19</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>102.95</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>103.19</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>102.95</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>281468682.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>283145846.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>283145846.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>351622846.6</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>414970230.06</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>414970230.06</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-104519583.1441735</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>281468682</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>281468682.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>99.08000000000001</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>103.5</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>103.2</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>103.2</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>289264312.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>275009623.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>275009623.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>442557432.7</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>412480726.12</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>412480726.12</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-103171216.5056498</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>289264312</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>289264312.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>100.42</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>103.72</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>103.4</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>103.72</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>103.4</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>220432535.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>268507044.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>268507044.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>577618774.1</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>409190484.56</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>409190484.56</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-98395538.21827114</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>220432535</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>220432535.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>101.72</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>103.96</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>103.6</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>103.96</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>103.6</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>360108082.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>286154072.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>286154072.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>1150276311.8</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>408529389.62</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>408529389.62</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-80684181.04993486</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>360108082</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>360108082.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>103.1</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>104.18</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>103.79</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>104.18</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>103.79</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>264455621.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>299044660.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>299044660.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>1304605197.0</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>411510598.5</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>411510598.5</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-67465901.52195692</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>264455621</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>264455621.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>104.9</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>104.18</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>104.03</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>104.18</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>104.03</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>240787568.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>420099846.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>420099846.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>1311901908.4</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>422014478.54</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>422014478.54</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-35924670.60620415</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>240787568</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>240787568.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>91.34</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>103.07</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>103.31</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>103.07</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>103.31</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>2683545818.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>5000685349.4</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>5000685349.4</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>4727097624.7</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>6863428946.3</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>6863428946.3</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-78239912.41163445</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>2683545818</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>2683545818.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>92.5</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>104.44</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>103.43</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>104.44</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>103.43</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>4682266073.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>5019578044.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>5019578044.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>4597307742.4</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>7180754379.14</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>7180754379.14</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>116188863.3358154</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>4682266073</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>4682266073.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>93.56</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>105.81</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>103.41</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>105.81</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>103.41</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>11515775721.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>4696916791.4</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>4696916791.4</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>4341077616.0</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>7241408797.74</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>7241408797.74</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>175646056.2487507</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>11515775721</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>11515775721.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>94.3</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>106.92</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>103.14</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>106.92</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>103.14</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>3032171594.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>3191641823.4</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>3191641823.4</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>3527299622.7</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>7285669264.58</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>7285669264.58</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-477849918.1702256</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>3032171594</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>3032171594.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>95.85999999999999</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>108.02</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>102.75</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>108.02</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>102.75</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>3089667541.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>4058514408.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>4058514408.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>3531039856.9</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>7317342463.3</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>7317342463.3</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-485391942.3698263</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>3089667541</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>3089667541.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>98.74</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>109.04</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>102.19</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>109.04</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>102.19</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>2778009293.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>4453509900.0</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>4453509900</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>3688316666.2</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>7280178623.2</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>7280178623.2</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-484991116.1774759</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>2778009293</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>2778009293.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>101.34</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>110.06</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>101.66</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>110.06</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>101.66</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>3068959808.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>4175037440.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>4175037440.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>3901577638.9</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>7265450343.64</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>7265450343.64</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-433705440.8963513</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>3068959808</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>3068959808.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>103.48</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>111.34</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>101.12</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>111.34</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>101.12</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>3989400881.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>3985238440.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>3985238440.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>3979054603.6</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>7220968787.64</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>7220968787.64</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-376123979.9270172</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>3989400881</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>3989400881.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>105.36</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>111.96</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>100.52</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>111.96</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>100.52</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>7366534520.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>3862957422.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>3862957422</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>4011436058.8</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>7171595467.56</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>7171595467.56</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-379050437.0805759</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>7366534520</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>7366534520.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>107.2</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>112.52</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>99.87</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>112.52</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>99.87</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>5064644998.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>3003565305.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>3003565305.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>4108066698.5</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>7070679471.22</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>7070679471.22</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-731529321.5827818</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>5064644998</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>5064644998.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>107.6</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>112.4</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>99.02</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>99.02</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>1385646995.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>2923123432.4</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>2923123432.4</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>4157974302.6</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>7004676232.68</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>7004676232.68</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-962313517.7436905</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>1385646995</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>1385646995.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>164.2</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>176.35</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>178.66</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>176.35</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>178.66</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>237989780.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>367839281.4</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>367839281.4</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>390785616.2</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>619088599.9</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>619088599.9</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-136007795.8903053</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>237989780</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>237989780.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>163.3</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>176.75</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>179.19</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>176.75</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>179.19</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>159879057.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>390309422.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>390309422.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>388711962.0</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>624204896.68</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>624204896.6799999</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-136759988.5246557</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>159879057</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>159879057.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>163.2</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>177.4</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>179.87</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>179.87</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>281592910.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>454120103.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>454120103</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>408623891.0</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>634139495.34</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>634139495.34</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-124581258.0907041</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>281592910</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>281592910.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>164.2</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>178.15</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>180.47</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>178.15</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>180.47</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>661439743.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>465917519.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>465917519</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>425236210.1</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>640116204.56</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>640116204.5599999</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-115774511.0746768</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>661439743</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>661439743.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>165.8</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>178.8</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>181.02</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>181.02</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>498294917.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>454526412.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>454526412</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>417725808.9</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>631196639.66</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>631196639.66</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-139756514.9062564</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>498294917</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>498294917.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>167.8</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>179.3</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>181.48</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>179.3</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>181.48</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>350340487.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>413731951.0</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>413731951</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>411216325.6</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>634370543.96</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>634370543.96</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-151545413.4904325</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>350340487</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>350340487.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>170.7</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>179.98</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>182.09</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>179.98</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>182.09</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>478932458.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>387114501.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>387114501.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>473719052.0</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>647350541.68</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>647350541.6799999</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-147122100.6288829</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>478932458</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>478932458.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>173.6</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>180.65</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>182.55</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>180.65</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>182.55</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>340579990.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>363127679.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>363127679</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>670451790.8</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>644918717.5</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>644918717.5</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-149326432.6970662</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>340579990</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>340579990.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>175.7</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>181.12</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>182.92</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>181.12</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>182.92</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>604484208.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>384554901.2</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>384554901.2</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>1377596235.0</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>654170853.0</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>654170853</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-132318912.9124327</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>604484208</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>604484208.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>177.8</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>181.55</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>183.34</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>181.55</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>183.34</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>294322612.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>380925205.8</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>380925205.8</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>1777576263.3</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>698405618.96</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>698405618.96</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-131572232.5446552</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>294322612</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>294322612.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>179.8</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>181.42</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>183.81</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>181.42</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>183.81</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>217253238.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>408700700.2</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>408700700.2</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>1872522206.7</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>746966653.34</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>746966653.34</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-92574938.4283781</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>217253238</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>217253238.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>

--- a/Result/checksun_type/電力系統.xlsx
+++ b/Result/checksun_type/電力系統.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX56"/>
+  <dimension ref="A1:CY55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -939,11 +939,16 @@
           <t>盤整震盪_前15日次數</t>
         </is>
       </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>多頭排列_前5日次數</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【c】;【x】看好</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -978,12 +983,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -998,7 +1003,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1093,12 +1098,12 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2025/02/14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>401.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1123,7 +1128,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-01-05 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1149,12 +1154,12 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1227,7 +1232,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>8922241883.408285</t>
+          <t>12427906968.294</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1253,12 +1258,12 @@
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>682042626.9439514</t>
+          <t>682042626.9438741</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>130778555.0567417</t>
+          <t>130778555.0567265</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1308,7 +1313,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1353,7 +1358,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>62.92</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1368,12 +1373,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>42.44</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>3156015</t>
+          <t>3143027</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1428,7 +1433,12 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1480,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1490,7 +1500,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1585,12 +1595,12 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2025/02/14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>401.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1615,7 +1625,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-01-05 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1641,12 +1651,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1719,7 +1729,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>8922241883.408285</t>
+          <t>12427906968.294</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1745,12 +1755,12 @@
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>782272458.1961713</t>
+          <t>782272458.1960828</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>325326917.2611217</t>
+          <t>325326917.2611027</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1800,7 +1810,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1845,7 +1855,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>62.92</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1860,12 +1870,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>42.44</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>3156015</t>
+          <t>3143027</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1920,7 +1930,12 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1962,12 +1977,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1982,7 +1997,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -2077,12 +2092,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2025/02/14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>401.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -2107,7 +2122,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2026-01-05 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -2133,12 +2148,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2211,7 +2226,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>8922241883.408285</t>
+          <t>12427906968.294</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -2237,12 +2252,12 @@
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>865353465.6389077</t>
+          <t>865353465.6388065</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>364644535.5080509</t>
+          <t>364644535.5080299</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2292,7 +2307,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2337,7 +2352,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>62.92</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2352,12 +2367,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>42.44</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>3156015</t>
+          <t>3143027</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2412,7 +2427,12 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2454,12 +2474,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2474,7 +2494,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2569,12 +2589,12 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2025/02/14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>401.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2599,7 +2619,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2026-01-05 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2625,12 +2645,12 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2703,7 +2723,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>8922241883.408285</t>
+          <t>12427906968.294</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2729,12 +2749,12 @@
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>956391452.9354271</t>
+          <t>956391452.9353113</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>655354488.6998081</t>
+          <t>655354488.6997833</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2784,7 +2804,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2829,7 +2849,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>62.92</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2844,12 +2864,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>42.44</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>3156015</t>
+          <t>3143027</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2904,7 +2924,12 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2971,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2966,7 +2991,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3061,12 +3086,12 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025/02/14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>401.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -3091,7 +3116,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-01-05 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -3117,12 +3142,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3185,7 +3210,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-13.32</t>
+          <t>-13.33</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3195,7 +3220,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>8922241883.408285</t>
+          <t>12427906968.294</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -3221,12 +3246,12 @@
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>1011125446.432812</t>
+          <t>1011125446.43268</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>666283506.6987514</t>
+          <t>666283506.6987247</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3276,7 +3301,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3321,7 +3346,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>62.92</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3336,12 +3361,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>42.44</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>3156015</t>
+          <t>3143027</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3396,7 +3421,12 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -3438,12 +3468,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -3458,7 +3488,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3553,12 +3583,12 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025/02/14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>401.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3583,7 +3613,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2026-01-05 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3609,12 +3639,12 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3687,7 +3717,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>8922241883.408285</t>
+          <t>12427906968.294</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -3713,12 +3743,12 @@
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>1073823980.929914</t>
+          <t>1073823980.929763</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>918943720.7437172</t>
+          <t>918943720.7436867</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3768,7 +3798,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3813,7 +3843,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>62.92</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3828,12 +3858,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>42.44</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>3156015</t>
+          <t>3143027</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3888,7 +3918,12 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -3930,12 +3965,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3950,7 +3985,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -4045,12 +4080,12 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025/02/14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>401.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -4075,7 +4110,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2026-01-05 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -4101,12 +4136,12 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4179,7 +4214,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>8922241883.408285</t>
+          <t>12427906968.294</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -4205,12 +4240,12 @@
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>1101984028.236495</t>
+          <t>1101984028.236322</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>1600917167.74568</t>
+          <t>1600917167.745644</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4260,7 +4295,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -4305,7 +4340,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>62.92</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4320,12 +4355,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>42.44</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>3156015</t>
+          <t>3143027</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4380,7 +4415,12 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -4422,12 +4462,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>-4.13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -4442,7 +4482,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4537,12 +4577,12 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025/02/14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>401.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4567,7 +4607,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2026-01-05 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4593,12 +4633,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4671,7 +4711,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>8922241883.408285</t>
+          <t>12427906968.294</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -4697,12 +4737,12 @@
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>1011268911.962098</t>
+          <t>1011268911.9619</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>2022637384.078993</t>
+          <t>2022637384.078951</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4752,7 +4792,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4777,7 +4817,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4797,7 +4837,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>62.92</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4812,12 +4852,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>42.44</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>3156015</t>
+          <t>3143027</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4872,7 +4912,12 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -4914,12 +4959,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -4934,7 +4979,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -5029,12 +5074,12 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025/02/14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>401.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -5059,7 +5104,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2026-01-05 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -5085,12 +5130,12 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5163,7 +5208,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>8922241883.408285</t>
+          <t>12427906968.294</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -5189,12 +5234,12 @@
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>827383735.213572</t>
+          <t>827383735.2133455</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>1795220034.052334</t>
+          <t>1795220034.052286</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5244,7 +5289,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -5269,7 +5314,7 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -5289,7 +5334,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>62.92</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5304,12 +5349,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>42.44</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>3156015</t>
+          <t>3143027</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5364,7 +5409,12 @@
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -5406,12 +5456,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.58</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -5426,7 +5476,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5521,12 +5571,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025/02/14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>401.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -5551,7 +5601,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2026-01-05 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -5577,12 +5627,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>234</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5655,7 +5705,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>8922241883.408285</t>
+          <t>12427906968.294</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -5681,12 +5731,12 @@
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>651413499.06107</t>
+          <t>651413499.0608108</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>1148762917.798094</t>
+          <t>1148762917.79804</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5736,7 +5786,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5781,7 +5831,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>62.92</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5796,12 +5846,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>42.44</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>3156015</t>
+          <t>3143027</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5856,29 +5906,34 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CY11" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】;【x】看好</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>4.69</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7555.816</t>
+          <t>3864.991</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5888,7 +5943,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1130.0</t>
+          <t>991.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5898,22 +5953,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>-6.98</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -5923,72 +5978,72 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-01-05 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-02-03 00:00:00</t>
+          <t>2026-02-02 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2025-10-07 00:00:00</t>
+          <t>2025-12-10 00:00:00</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-10-20 00:00:00</t>
+          <t>2025-12-29 00:00:00</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1010.0</t>
+          <t>817.0</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1215.0</t>
+          <t>942.0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1010.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>987.0</t>
+          <t>779.0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>1015.0</t>
+          <t>778.0</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>11.88</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.00</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025/05/22</t>
+          <t>2025/05/23</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>378.0</t>
+          <t>479.0</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -5998,67 +6053,67 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2025/11/27</t>
+          <t>2025/09/08</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
+          <t>629.0</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
           <t>942.0</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>2025/02/14</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>401.0</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>2026/02/03</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>1215.0</t>
-        </is>
-      </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2025/12/12</t>
+          <t>2025/12/29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>938.0</t>
+          <t>778.0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2026-01-05 00:00:00</t>
+          <t>2026-01-13 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>13.78</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6069,156 +6124,156 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>11407</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>98.55</t>
+          <t>17.87</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="AV12" t="n">
-        <v>7.62</v>
+        <v>2.65</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>14.47</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1096.0</t>
+          <t>973.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1018.4</v>
+        <v>947.9</v>
       </c>
       <c r="BA12" t="n">
-        <v>972.02</v>
+        <v>828.0599999999999</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>973.11</t>
+          <t>772.05</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>-15.74</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>40.99</v>
+        <v>49.82</v>
       </c>
       <c r="BE12" t="n">
-        <v>28.37</v>
+        <v>59.13</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>64.81</t>
+          <t>65.14</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-56.23</t>
+          <t>-9.23</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2025/12/24</t>
+          <t>2026/01/12</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>8922241883.408285</t>
+          <t>4675997349.950199</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>8487601840.0</t>
+          <t>3755240297.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>13759881328.4</v>
+        <v>4269734798.6</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>13239152071.6</t>
+          <t>4590271769.3</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>11312850650.8</v>
+        <v>4693942391.54</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>520729256</t>
+          <t>-320536970</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>560986332.0179747</t>
+          <t>-39995843.77833214</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>572902443.5849628</t>
+          <t>-411743274.1713076</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>8487601840.0</t>
+          <t>3755240297.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1015.0</t>
+          <t>772.0</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2026/01/09</t>
+          <t>2025/11/04</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>11.33</t>
+          <t>28.37</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>電子零組件業</t>
+          <t>電機機械</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
@@ -6228,134 +6283,139 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>6.21790530768367</t>
+          <t>96.81819631152293</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>38.58583304817382</t>
+          <t>10.85414157538786</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>31.75552339723058</t>
+          <t>20.88959147649935</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>35.72</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>57.87</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>63.18</t>
+          <t>72.71</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>34.87%</t>
+          <t>41.69%</t>
         </is>
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>16.50%</t>
+          <t>20.62%</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>41.31</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>3156015</t>
+          <t>313037</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>電源及零組件53.00%、基礎設施24.00%、自動化業務12.00%、交通業11.00% (2024年)</t>
+          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>台達電-電子零組件業-上市</t>
+          <t>華城-電機機械-上市</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>電子零組件業右上上市</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>1105.0</t>
+          <t>939.0</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>1140.0</t>
+          <t>992.0</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>1100.0</t>
+          <t>939.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>1130.0</t>
+          <t>991.0</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
         <is>
-          <t>92.68</t>
+          <t>27.74</t>
         </is>
       </c>
       <c r="CV12" t="inlineStr">
         <is>
-          <t>** 休閒娛樂 - 休閒車業** 半導體 - 生產製程及檢測設備、IC模組、IC通路、LED驅動IC、消費性IC、微控制器IC、電源管理IC** 電腦及週邊設備 - 電源供應器、散熱片、風扇馬達、散熱模組、筆記型電腦、桌上型電腦、精簡型電腦、安全監控系統** 平面顯示器 - 其他零組件** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、光通訊設備(如光纖電纜、光傳輸設備)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 被動元件 - 電阻器、電容器、電感器** 電機機械 - 傳動元件、電控元件、專用機械(如紡織成衣生產用機械、食品飲料生產用機械、農林用機械等)、輸送機械及零配件** 軟體服務 - 應用/系統軟體設計開發** 建材營造 - 機電工程** 其他 - 特殊照明業** 汽車 - 其他** 人工智慧 - 系統整合、顧問諮詢、領域解決方案、智慧設備、機器學習、電腦視覺、運算設備** 雲端運算 - 電力設備、冷卻設備、設備管理軟體、系統整合、顧問諮詢、設備安裝服務、伺服器、SaaS** 大數據 - 系統整合、顧問諮詢、領域解決方案、運算元件與設備** 太空衛星科技 - 天線/射頻基頻** 體驗科技 - 電池模組** LED照明產業 - 燈具/應用** 電動車輛產業 - 鋰電池材料、大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件、電動汽車、電動機車、電動自行車** 太陽能產業 - 太陽能發電設備/系統及系統工程、太陽能電廠** 風力發電 - 監控系統、電力系統** 能源元件 - 電池芯、電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施、能源管理服務、系統整合服務** 醫療器材 - 塑化材料、生物檢測、其他、醫療器材代理</t>
+          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
         </is>
       </c>
       <c r="CW12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY12" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【c】;【x】看好</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6390,12 +6450,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -6410,7 +6470,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -6505,12 +6565,12 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025/04/01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -6535,7 +6595,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-13 00:00:00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -6561,12 +6621,12 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6624,12 +6684,12 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>80.59</t>
+          <t>65.14</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-23.74</t>
+          <t>-5.65</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6639,7 +6699,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>5705438909.37574</t>
+          <t>4675997349.950199</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -6665,12 +6725,12 @@
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>27594598.11131342</t>
+          <t>27594598.11129976</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-366446603.0707283</t>
+          <t>-366446603.0707312</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -6755,7 +6815,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6765,7 +6825,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>69.48</t>
+          <t>72.71</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6780,12 +6840,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>299138</t>
+          <t>313037</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6840,7 +6900,12 @@
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY13" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6947,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>4.94</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -6902,7 +6967,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6997,12 +7062,12 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2025/04/01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -7027,7 +7092,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-13 00:00:00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -7053,12 +7118,12 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -7116,12 +7181,12 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>80.59</t>
+          <t>65.14</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-20.81</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7131,7 +7196,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>5705438909.37574</t>
+          <t>4675997349.950199</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -7157,12 +7222,12 @@
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>99238452.87168464</t>
+          <t>99238452.87166902</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-491671015.6030922</t>
+          <t>-491671015.6030951</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -7247,7 +7312,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7257,7 +7322,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>69.48</t>
+          <t>72.71</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7272,12 +7337,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>299138</t>
+          <t>313037</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7332,7 +7397,12 @@
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY14" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7444,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -7394,7 +7464,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -7489,12 +7559,12 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2025/04/01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -7519,7 +7589,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-13 00:00:00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -7545,12 +7615,12 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -7608,12 +7678,12 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>80.59</t>
+          <t>65.14</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-19.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7623,7 +7693,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>5705438909.37574</t>
+          <t>4675997349.950199</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -7649,12 +7719,12 @@
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>206676538.0489168</t>
+          <t>206676538.0488989</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-421739997.7706451</t>
+          <t>-421739997.770648</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -7739,7 +7809,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7749,7 +7819,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>69.48</t>
+          <t>72.71</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7764,12 +7834,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>299138</t>
+          <t>313037</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7824,7 +7894,12 @@
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY15" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7941,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-7.18</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -7886,7 +7961,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7981,12 +8056,12 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2025/04/01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -8011,7 +8086,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-13 00:00:00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -8037,12 +8112,12 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -8100,12 +8175,12 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>80.59</t>
+          <t>65.14</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-19.59</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8115,7 +8190,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>5705438909.37574</t>
+          <t>4675997349.950199</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -8141,12 +8216,12 @@
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>320934090.0161099</t>
+          <t>320934090.0160893</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-329809363.2681971</t>
+          <t>-329809363.2682009</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -8231,7 +8306,7 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8241,7 +8316,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>69.48</t>
+          <t>72.71</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8256,12 +8331,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>299138</t>
+          <t>313037</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8316,7 +8391,12 @@
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY16" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -8358,12 +8438,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -8378,7 +8458,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -8473,12 +8553,12 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2025/04/01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -8503,7 +8583,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-13 00:00:00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -8529,12 +8609,12 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -8592,12 +8672,12 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>80.59</t>
+          <t>65.14</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-22.10</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8607,7 +8687,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>5705438909.37574</t>
+          <t>4675997349.950199</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -8633,12 +8713,12 @@
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>439251081.5223475</t>
+          <t>439251081.5223238</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-297961893.7551203</t>
+          <t>-297961893.755125</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -8723,7 +8803,7 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8733,7 +8813,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>69.48</t>
+          <t>72.71</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8748,12 +8828,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>299138</t>
+          <t>313037</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8808,7 +8888,12 @@
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY17" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -8850,12 +8935,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-7.18</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -8870,7 +8955,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -8965,12 +9050,12 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2025/04/01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -8995,7 +9080,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-13 00:00:00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -9021,12 +9106,12 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -9084,12 +9169,12 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>80.59</t>
+          <t>65.14</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-25.99</t>
+          <t>-8.44</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9099,7 +9184,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>5705438909.37574</t>
+          <t>4675997349.950199</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -9125,12 +9210,12 @@
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>573289804.300069</t>
+          <t>573289804.3000418</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-98363687.67375755</t>
+          <t>-98363687.67376328</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -9215,7 +9300,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9225,7 +9310,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>69.48</t>
+          <t>72.71</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9240,12 +9325,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>299138</t>
+          <t>313037</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9300,7 +9385,12 @@
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY18" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -9342,12 +9432,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-7.71</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -9362,7 +9452,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -9457,12 +9547,12 @@
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2025/04/01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -9487,7 +9577,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-13 00:00:00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -9513,12 +9603,12 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -9576,12 +9666,12 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>80.59</t>
+          <t>65.14</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-30.72</t>
+          <t>-14.29</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9591,7 +9681,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>5705438909.37574</t>
+          <t>4675997349.950199</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -9617,12 +9707,12 @@
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>695408621.0225829</t>
+          <t>695408621.0225518</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>285328602.359395</t>
+          <t>285328602.3593884</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -9707,7 +9797,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9717,7 +9807,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>69.48</t>
+          <t>72.71</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9732,12 +9822,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>299138</t>
+          <t>313037</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9792,7 +9882,12 @@
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY19" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9929,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-8.76</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -9854,7 +9949,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -9949,12 +10044,12 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2025/04/01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -9979,7 +10074,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-13 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
@@ -10005,12 +10100,12 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -10068,12 +10163,12 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>80.59</t>
+          <t>65.14</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-36.89</t>
+          <t>-21.92</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -10083,7 +10178,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>5705438909.37574</t>
+          <t>4675997349.950199</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
@@ -10109,12 +10204,12 @@
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>769968624.4158897</t>
+          <t>769968624.4158543</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>614551550.5367775</t>
+          <t>614551550.5367699</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -10189,7 +10284,7 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -10199,7 +10294,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10209,7 +10304,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>69.48</t>
+          <t>72.71</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10224,12 +10319,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>299138</t>
+          <t>313037</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10284,7 +10379,12 @@
       </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY20" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -10326,12 +10426,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-14.04</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -10346,7 +10446,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -10441,12 +10541,12 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2025/04/01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -10471,7 +10571,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-13 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -10497,12 +10597,12 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10560,12 +10660,12 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>80.59</t>
+          <t>65.14</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-44.43</t>
+          <t>-31.25</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10575,7 +10675,7 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>5705438909.37574</t>
+          <t>4675997349.950199</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
@@ -10601,12 +10701,12 @@
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>798226274.2120919</t>
+          <t>798226274.2120515</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>979567607.5567236</t>
+          <t>979567607.556715</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -10681,7 +10781,7 @@
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -10691,7 +10791,7 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10701,7 +10801,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>69.48</t>
+          <t>72.71</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10716,12 +10816,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>299138</t>
+          <t>313037</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10776,7 +10876,12 @@
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY21" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -10818,12 +10923,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-8.24</t>
+          <t>-3.43</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -10838,7 +10943,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -10933,12 +11038,12 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2025/04/01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -10963,7 +11068,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-13 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -10989,12 +11094,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>160</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -11052,12 +11157,12 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>80.59</t>
+          <t>65.14</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-53.00</t>
+          <t>-41.85</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -11067,7 +11172,7 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>5705438909.37574</t>
+          <t>4675997349.950199</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
@@ -11093,12 +11198,12 @@
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>765255122.6948862</t>
+          <t>765255122.69484</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>1072645695.886765</t>
+          <t>1072645695.886755</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -11183,7 +11288,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11193,7 +11298,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>69.48</t>
+          <t>72.71</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11208,12 +11313,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>299138</t>
+          <t>313037</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11268,29 +11373,34 @@
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CY22" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8949.618</t>
+          <t>4668.385</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11300,7 +11410,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1005.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11310,22 +11420,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-6.12</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>-60.24</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -11335,7 +11445,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-01-12 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -11345,62 +11455,62 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2025-12-10 00:00:00</t>
+          <t>2025-06-12 00:00:00</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2025-12-29 00:00:00</t>
+          <t>2025-06-20 00:00:00</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>817.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>942.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>817.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>779.0</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>778.0</t>
+          <t>111.5</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>6.69</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025/05/23</t>
+          <t>2025/11/12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>479.0</t>
+          <t>101.5</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -11410,27 +11520,27 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>2025/09/08</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>629.0</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2025/04/01</t>
+          <t>2025/09/26</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>430.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -11440,37 +11550,37 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>942.0</t>
+          <t>121.5</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2025/12/29</t>
+          <t>2026/01/05</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>778.0</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11481,151 +11591,151 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>21.43</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>99.71</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>6.17</v>
+        <v>0.08</v>
       </c>
       <c r="AV23" t="n">
-        <v>16.03</v>
+        <v>3.69</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>12.86</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>946.6</t>
+          <t>125.9</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>815.85</v>
+        <v>121.42</v>
       </c>
       <c r="BA23" t="n">
-        <v>768.3200000000001</v>
+        <v>107.58</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>712.55</t>
+          <t>105.53</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>73.67</t>
+          <t>-13.94</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>55</v>
+        <v>6.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>31.67</v>
+        <v>7.78</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>80.59</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-60.70</t>
+          <t>-6.59</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026/01/12</t>
+          <t>2026/01/14</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>5705438909.37574</t>
+          <t>969588383.4023905</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>8852138170.0</t>
+          <t>587222065.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>10926475421.4</v>
+        <v>1047411780.4</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>7873540687.9</t>
+          <t>2634416617.4</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>4108092195.64</v>
+        <v>1091753503.96</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-1587004837</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>709365927.5690901</t>
+          <t>184422715.7149106</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>1305333023.540867</t>
+          <t>-246702457.446933</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>8852138170.0</t>
+          <t>587222065.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>772.0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2025/11/04</t>
+          <t>2026/01/15</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>30.18</t>
+          <t>21.15</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="BX23" t="inlineStr">
@@ -11640,82 +11750,82 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
         <is>
-          <t>96.81819631152293</t>
+          <t>15.10114342591251</t>
         </is>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>10.85414157538786</t>
+          <t>10.8071733851868</t>
         </is>
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>20.88959147649935</t>
+          <t>19.54664578957038</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>36.23</t>
+          <t>5.68</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>10.38</t>
         </is>
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>69.48</t>
+          <t>41.72</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
         <is>
-          <t>41.69%</t>
+          <t>17.74%</t>
         </is>
       </c>
       <c r="CK23" t="inlineStr">
         <is>
-          <t>20.62%</t>
+          <t>9.59%</t>
         </is>
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>299138</t>
+          <t>34412</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
         <is>
-          <t>變壓器72.13%、其他9.96%、配電盤8.13%、工程承包6.87%、配電器材2.84%、電力0.07% (2024年)</t>
+          <t>電機26.81%、電子產品24.03%、工程15.07%、變壓器12.05%、電機器材11.28%、代理及其他10.76% (2024年)</t>
         </is>
       </c>
       <c r="CO23" t="inlineStr">
         <is>
-          <t>華城-電機機械-上市</t>
+          <t>亞力-電機機械-上市</t>
         </is>
       </c>
       <c r="CP23" t="inlineStr">
@@ -11725,42 +11835,47 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>960.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>1005.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>956.0</t>
+          <t>122.5</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>1005.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
         <is>
-          <t>27.74</t>
+          <t>22.17</t>
         </is>
       </c>
       <c r="CV23" t="inlineStr">
         <is>
-          <t>** 電機機械 - 機電系統工程** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 汽電共生 - 配電系統、變壓器** 風力發電 - 電力系統** 智慧電網 - 高/低壓輸電設施、配電管理設施、電網營造</t>
+          <t>** 電機機械 - 機電系統工程** 汽電共生 - 配電系統** 風力發電 - 電力系統</t>
         </is>
       </c>
       <c r="CW23" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY23" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11922,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -11822,7 +11937,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -11947,7 +12062,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
@@ -11973,12 +12088,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -12036,12 +12151,12 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-46.03</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -12051,7 +12166,7 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>1923511594.677515</t>
+          <t>969588383.4023905</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -12077,12 +12192,12 @@
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>262809110.8352448</t>
+          <t>262809110.8352458</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-159698433.9717684</t>
+          <t>-159698433.9717674</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
@@ -12132,7 +12247,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -12192,7 +12307,7 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
@@ -12252,7 +12367,12 @@
       </c>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY24" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12419,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -12314,7 +12434,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -12439,7 +12559,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
@@ -12465,12 +12585,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12528,12 +12648,12 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-44.73</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12543,7 +12663,7 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>1923511594.677515</t>
+          <t>969588383.4023905</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
@@ -12569,12 +12689,12 @@
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>339628664.43652</t>
+          <t>339628664.436521</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>-88321056.15111113</t>
+          <t>-88321056.15111065</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
@@ -12624,7 +12744,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -12684,7 +12804,7 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
@@ -12744,7 +12864,12 @@
       </c>
       <c r="CX25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY25" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12916,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -12806,7 +12931,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -12931,7 +13056,7 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
@@ -12957,12 +13082,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -13020,12 +13145,12 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-44.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -13035,7 +13160,7 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>1923511594.677515</t>
+          <t>969588383.4023905</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
@@ -13061,12 +13186,12 @@
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>417437704.543362</t>
+          <t>417437704.5433631</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>58103291.95522404</t>
+          <t>58103291.95522451</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
@@ -13116,7 +13241,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13176,7 +13301,7 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
@@ -13236,7 +13361,12 @@
       </c>
       <c r="CX26" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CY26" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -13283,7 +13413,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -13298,7 +13428,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -13423,7 +13553,7 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
@@ -13449,12 +13579,12 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -13512,12 +13642,12 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-45.39</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13527,7 +13657,7 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>1923511594.677515</t>
+          <t>969588383.4023905</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
@@ -13553,12 +13683,12 @@
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>482771234.1048417</t>
+          <t>482771234.1048428</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>215875585.0730166</t>
+          <t>215875585.0730171</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
@@ -13608,7 +13738,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13668,7 +13798,7 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
@@ -13728,7 +13858,12 @@
       </c>
       <c r="CX27" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="CY27" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -13775,7 +13910,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -13790,7 +13925,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -13915,7 +14050,7 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
@@ -13941,12 +14076,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -14004,12 +14139,12 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-48.83</t>
+          <t>-8.35</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -14019,7 +14154,7 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>1923511594.677515</t>
+          <t>969588383.4023905</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
@@ -14045,12 +14180,12 @@
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>531297715.7469917</t>
+          <t>531297715.7469929</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>396248360.0958266</t>
+          <t>396248360.0958271</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
@@ -14100,7 +14235,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -14160,7 +14295,7 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
@@ -14220,7 +14355,12 @@
       </c>
       <c r="CX28" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="CY28" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -14267,7 +14407,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -14282,7 +14422,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -14407,7 +14547,7 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
@@ -14433,12 +14573,12 @@
       <c r="AP29" t="inlineStr"/>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -14496,12 +14636,12 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>-53.77</t>
+          <t>-17.20</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
@@ -14511,7 +14651,7 @@
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>1923511594.677515</t>
+          <t>969588383.4023905</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr">
@@ -14537,12 +14677,12 @@
       </c>
       <c r="BO29" t="inlineStr">
         <is>
-          <t>555852144.0472035</t>
+          <t>555852144.047205</t>
         </is>
       </c>
       <c r="BP29" t="inlineStr">
         <is>
-          <t>495197671.0178471</t>
+          <t>495197671.0178475</t>
         </is>
       </c>
       <c r="BQ29" t="inlineStr">
@@ -14592,7 +14732,7 @@
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -14652,7 +14792,7 @@
       </c>
       <c r="CL29" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM29" t="inlineStr">
@@ -14712,7 +14852,12 @@
       </c>
       <c r="CX29" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="CY29" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -14759,7 +14904,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -14774,7 +14919,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -14899,7 +15044,7 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
@@ -14925,12 +15070,12 @@
       <c r="AP30" t="inlineStr"/>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -14988,12 +15133,12 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>-59.48</t>
+          <t>-27.44</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
@@ -15003,7 +15148,7 @@
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>1923511594.677515</t>
+          <t>969588383.4023905</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr">
@@ -15029,12 +15174,12 @@
       </c>
       <c r="BO30" t="inlineStr">
         <is>
-          <t>566880230.052541</t>
+          <t>566880230.0525427</t>
         </is>
       </c>
       <c r="BP30" t="inlineStr">
         <is>
-          <t>753896151.5129533</t>
+          <t>753896151.5129538</t>
         </is>
       </c>
       <c r="BQ30" t="inlineStr">
@@ -15084,7 +15229,7 @@
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -15144,7 +15289,7 @@
       </c>
       <c r="CL30" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM30" t="inlineStr">
@@ -15204,7 +15349,12 @@
       </c>
       <c r="CX30" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="CY30" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -15251,7 +15401,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -15266,7 +15416,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -15391,7 +15541,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
@@ -15417,12 +15567,12 @@
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -15480,12 +15630,12 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>-66.73</t>
+          <t>-40.41</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
@@ -15495,7 +15645,7 @@
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>1923511594.677515</t>
+          <t>969588383.4023905</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr">
@@ -15521,7 +15671,7 @@
       </c>
       <c r="BO31" t="inlineStr">
         <is>
-          <t>532877335.2415569</t>
+          <t>532877335.2415588</t>
         </is>
       </c>
       <c r="BP31" t="inlineStr">
@@ -15576,7 +15726,7 @@
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -15601,7 +15751,7 @@
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
@@ -15636,7 +15786,7 @@
       </c>
       <c r="CL31" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM31" t="inlineStr">
@@ -15696,7 +15846,12 @@
       </c>
       <c r="CX31" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="CY31" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -15743,7 +15898,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -15758,7 +15913,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -15883,7 +16038,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
@@ -15909,12 +16064,12 @@
       <c r="AP32" t="inlineStr"/>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
@@ -15972,12 +16127,12 @@
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>-74.64</t>
+          <t>-54.58</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
@@ -15987,7 +16142,7 @@
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>1923511594.677515</t>
+          <t>969588383.4023905</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr">
@@ -16013,7 +16168,7 @@
       </c>
       <c r="BO32" t="inlineStr">
         <is>
-          <t>441467874.3786322</t>
+          <t>441467874.3786343</t>
         </is>
       </c>
       <c r="BP32" t="inlineStr">
@@ -16068,7 +16223,7 @@
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -16093,7 +16248,7 @@
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
@@ -16128,7 +16283,7 @@
       </c>
       <c r="CL32" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM32" t="inlineStr">
@@ -16188,7 +16343,12 @@
       </c>
       <c r="CX32" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="CY32" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -16235,7 +16395,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -16250,7 +16410,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -16375,7 +16535,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
@@ -16401,12 +16561,12 @@
       <c r="AP33" t="inlineStr"/>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -16464,12 +16624,12 @@
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>-82.23</t>
+          <t>-68.18</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
@@ -16479,7 +16639,7 @@
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>1923511594.677515</t>
+          <t>969588383.4023905</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr">
@@ -16505,12 +16665,12 @@
       </c>
       <c r="BO33" t="inlineStr">
         <is>
-          <t>304835157.6250464</t>
+          <t>304835157.6250488</t>
         </is>
       </c>
       <c r="BP33" t="inlineStr">
         <is>
-          <t>729785070.5199654</t>
+          <t>729785070.5199661</t>
         </is>
       </c>
       <c r="BQ33" t="inlineStr">
@@ -16560,7 +16720,7 @@
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -16620,7 +16780,7 @@
       </c>
       <c r="CL33" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM33" t="inlineStr">
@@ -16680,29 +16840,34 @@
       </c>
       <c r="CX33" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="CY33" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1504</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>34598.589</t>
+          <t>8631.537</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -16712,7 +16877,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -16722,167 +16887,167 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>84.72</t>
+          <t>-41.45</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
+          <t>2025-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>101.5</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>-20.48</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>25.62</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025/05/21</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>52.4</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>2025/06/30</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>47.3</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>2026/01/30</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>2025/10/14</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
           <t>2026-01-16 00:00:00</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2026-02-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2025-06-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>2025-06-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>121.5</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>114.0</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>115.5</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>111.5</t>
-        </is>
-      </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>11.40</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>4.53</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>101.5</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>95.2</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
-        <is>
-          <t>2025/09/26</t>
-        </is>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>100.5</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr">
-        <is>
-          <t>2026/02/02</t>
-        </is>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>121.5</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>2026/01/05</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>96.9</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>2026-01-19 00:00:00</t>
-        </is>
-      </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>47.99</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>5.66</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -16893,151 +17058,151 @@
       <c r="AP34" t="inlineStr"/>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="AU34" t="n">
-        <v>10.72</v>
+        <v>0.9</v>
       </c>
       <c r="AV34" t="n">
-        <v>11.16</v>
+        <v>-4.01</v>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>114.7</t>
+          <t>81.96000000000001</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>103.18</v>
+        <v>85.38</v>
       </c>
       <c r="BA34" t="n">
-        <v>100.07</v>
+        <v>85.62</v>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>101.14</t>
+          <t>94.01</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>173.72</t>
+          <t>-76.01</t>
         </is>
       </c>
       <c r="BD34" t="n">
-        <v>4.52</v>
+        <v>-1.2</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.65</v>
+        <v>-0.68</v>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>14.92</t>
+          <t>9.92</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>-88.92</t>
+          <t>-106.85</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026/01/14</t>
+          <t>2025/12/11</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>1923511594.677515</t>
+          <t>3608269246.254</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr">
         <is>
-          <t>4317679461.0</t>
+          <t>711861375.0</t>
         </is>
       </c>
       <c r="BK34" t="n">
-        <v>3068379347.8</v>
+        <v>1508478018.2</v>
       </c>
       <c r="BL34" t="inlineStr">
         <is>
-          <t>1661055431.8</t>
+          <t>2576194646.2</t>
         </is>
       </c>
       <c r="BM34" t="n">
-        <v>547846754.02</v>
+        <v>2280147951.22</v>
       </c>
       <c r="BN34" t="inlineStr">
         <is>
-          <t>1407323916</t>
+          <t>-1067716628</t>
         </is>
       </c>
       <c r="BO34" t="inlineStr">
         <is>
-          <t>227571537.0986975</t>
+          <t>-2383770.836727075</t>
         </is>
       </c>
       <c r="BP34" t="inlineStr">
         <is>
-          <t>662824590.3894112</t>
+          <t>-384325383.5689278</t>
         </is>
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>4317679461.0</t>
+          <t>711861375.0</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
         <is>
-          <t>2026/01/15</t>
+          <t>2025/08/11</t>
         </is>
       </c>
       <c r="BU34" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="BV34" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="BW34" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="BX34" t="inlineStr">
@@ -17052,82 +17217,82 @@
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
         <is>
-          <t>15.10114342591251</t>
+          <t>20.96595910135787</t>
         </is>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>10.8071733851868</t>
+          <t>15.63698930879905</t>
         </is>
       </c>
       <c r="CC34" t="inlineStr">
         <is>
-          <t>19.54664578957038</t>
+          <t>6.485882553210391</t>
         </is>
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>5.73</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">
         <is>
-          <t>10.38</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="CI34" t="inlineStr">
         <is>
-          <t>41.72</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="CJ34" t="inlineStr">
         <is>
-          <t>17.74%</t>
+          <t>24.44%</t>
         </is>
       </c>
       <c r="CK34" t="inlineStr">
         <is>
-          <t>9.59%</t>
+          <t>11.24%</t>
         </is>
       </c>
       <c r="CL34" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM34" t="inlineStr">
         <is>
-          <t>34412</t>
+          <t>196532</t>
         </is>
       </c>
       <c r="CN34" t="inlineStr">
         <is>
-          <t>電機26.81%、電子產品24.03%、工程15.07%、變壓器12.05%、電機器材11.28%、代理及其他10.76% (2024年)</t>
+          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
         </is>
       </c>
       <c r="CO34" t="inlineStr">
         <is>
-          <t>亞力-電機機械-上市</t>
+          <t>東元-電機機械-上市</t>
         </is>
       </c>
       <c r="CP34" t="inlineStr">
@@ -17137,42 +17302,47 @@
       </c>
       <c r="CQ34" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="CR34" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="CS34" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="CT34" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="CU34" t="inlineStr">
         <is>
-          <t>22.17</t>
+          <t>37.41</t>
         </is>
       </c>
       <c r="CV34" t="inlineStr">
         <is>
-          <t>** 電機機械 - 機電系統工程** 汽電共生 - 配電系統** 風力發電 - 電力系統</t>
+          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
         </is>
       </c>
       <c r="CW34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="CX34" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="CY34" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -17214,12 +17384,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -17234,7 +17404,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -17359,7 +17529,7 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>2026-01-15 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
@@ -17385,12 +17555,12 @@
       <c r="AP35" t="inlineStr"/>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
@@ -17463,7 +17633,7 @@
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>2260026082.286561</t>
+          <t>3608269246.254</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr">
@@ -17489,12 +17659,12 @@
       </c>
       <c r="BO35" t="inlineStr">
         <is>
-          <t>67060158.7509492</t>
+          <t>67060158.75094578</t>
         </is>
       </c>
       <c r="BP35" t="inlineStr">
         <is>
-          <t>-299065700.7246289</t>
+          <t>-299065700.7246294</t>
         </is>
       </c>
       <c r="BQ35" t="inlineStr">
@@ -17579,7 +17749,7 @@
       </c>
       <c r="CG35" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="CH35" t="inlineStr">
@@ -17589,7 +17759,7 @@
       </c>
       <c r="CI35" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="CJ35" t="inlineStr">
@@ -17604,12 +17774,12 @@
       </c>
       <c r="CL35" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM35" t="inlineStr">
         <is>
-          <t>194155</t>
+          <t>196532</t>
         </is>
       </c>
       <c r="CN35" t="inlineStr">
@@ -17664,7 +17834,12 @@
       </c>
       <c r="CX35" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="CY35" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -17706,12 +17881,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -17726,7 +17901,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -17851,7 +18026,7 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>2026-01-15 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
@@ -17877,12 +18052,12 @@
       <c r="AP36" t="inlineStr"/>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
@@ -17955,7 +18130,7 @@
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>2260026082.286561</t>
+          <t>3608269246.254</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr">
@@ -17981,12 +18156,12 @@
       </c>
       <c r="BO36" t="inlineStr">
         <is>
-          <t>133628496.837418</t>
+          <t>133628496.837414</t>
         </is>
       </c>
       <c r="BP36" t="inlineStr">
         <is>
-          <t>-203498081.4926085</t>
+          <t>-203498081.4926095</t>
         </is>
       </c>
       <c r="BQ36" t="inlineStr">
@@ -18071,7 +18246,7 @@
       </c>
       <c r="CG36" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="CH36" t="inlineStr">
@@ -18081,7 +18256,7 @@
       </c>
       <c r="CI36" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="CJ36" t="inlineStr">
@@ -18096,12 +18271,12 @@
       </c>
       <c r="CL36" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM36" t="inlineStr">
         <is>
-          <t>194155</t>
+          <t>196532</t>
         </is>
       </c>
       <c r="CN36" t="inlineStr">
@@ -18156,7 +18331,12 @@
       </c>
       <c r="CX36" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="CY36" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -18198,12 +18378,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -18218,7 +18398,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -18343,7 +18523,7 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>2026-01-15 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
@@ -18369,12 +18549,12 @@
       <c r="AP37" t="inlineStr"/>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
@@ -18447,7 +18627,7 @@
       </c>
       <c r="BI37" t="inlineStr">
         <is>
-          <t>2260026082.286561</t>
+          <t>3608269246.254</t>
         </is>
       </c>
       <c r="BJ37" t="inlineStr">
@@ -18473,12 +18653,12 @@
       </c>
       <c r="BO37" t="inlineStr">
         <is>
-          <t>194924238.3519682</t>
+          <t>194924238.3519637</t>
         </is>
       </c>
       <c r="BP37" t="inlineStr">
         <is>
-          <t>-145053580.9649868</t>
+          <t>-145053580.9649878</t>
         </is>
       </c>
       <c r="BQ37" t="inlineStr">
@@ -18563,7 +18743,7 @@
       </c>
       <c r="CG37" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="CH37" t="inlineStr">
@@ -18573,7 +18753,7 @@
       </c>
       <c r="CI37" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="CJ37" t="inlineStr">
@@ -18588,12 +18768,12 @@
       </c>
       <c r="CL37" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM37" t="inlineStr">
         <is>
-          <t>194155</t>
+          <t>196532</t>
         </is>
       </c>
       <c r="CN37" t="inlineStr">
@@ -18648,7 +18828,12 @@
       </c>
       <c r="CX37" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="CY37" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -18690,12 +18875,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-3.43</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -18710,7 +18895,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -18835,7 +19020,7 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>2026-01-15 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
@@ -18861,12 +19046,12 @@
       <c r="AP38" t="inlineStr"/>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
@@ -18939,7 +19124,7 @@
       </c>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>2260026082.286561</t>
+          <t>3608269246.254</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr">
@@ -18965,12 +19150,12 @@
       </c>
       <c r="BO38" t="inlineStr">
         <is>
-          <t>256738387.3186873</t>
+          <t>256738387.3186822</t>
         </is>
       </c>
       <c r="BP38" t="inlineStr">
         <is>
-          <t>-94266195.28392029</t>
+          <t>-94266195.28392124</t>
         </is>
       </c>
       <c r="BQ38" t="inlineStr">
@@ -19055,7 +19240,7 @@
       </c>
       <c r="CG38" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="CH38" t="inlineStr">
@@ -19065,7 +19250,7 @@
       </c>
       <c r="CI38" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="CJ38" t="inlineStr">
@@ -19080,12 +19265,12 @@
       </c>
       <c r="CL38" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM38" t="inlineStr">
         <is>
-          <t>194155</t>
+          <t>196532</t>
         </is>
       </c>
       <c r="CN38" t="inlineStr">
@@ -19140,7 +19325,12 @@
       </c>
       <c r="CX38" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="CY38" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -19182,12 +19372,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -19202,7 +19392,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -19327,7 +19517,7 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>2026-01-15 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
@@ -19353,12 +19543,12 @@
       <c r="AP39" t="inlineStr"/>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
@@ -19431,7 +19621,7 @@
       </c>
       <c r="BI39" t="inlineStr">
         <is>
-          <t>2260026082.286561</t>
+          <t>3608269246.254</t>
         </is>
       </c>
       <c r="BJ39" t="inlineStr">
@@ -19457,12 +19647,12 @@
       </c>
       <c r="BO39" t="inlineStr">
         <is>
-          <t>320557402.3373432</t>
+          <t>320557402.3373373</t>
         </is>
       </c>
       <c r="BP39" t="inlineStr">
         <is>
-          <t>34362190.16345787</t>
+          <t>34362190.16345644</t>
         </is>
       </c>
       <c r="BQ39" t="inlineStr">
@@ -19547,7 +19737,7 @@
       </c>
       <c r="CG39" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="CH39" t="inlineStr">
@@ -19557,7 +19747,7 @@
       </c>
       <c r="CI39" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="CJ39" t="inlineStr">
@@ -19572,12 +19762,12 @@
       </c>
       <c r="CL39" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM39" t="inlineStr">
         <is>
-          <t>194155</t>
+          <t>196532</t>
         </is>
       </c>
       <c r="CN39" t="inlineStr">
@@ -19632,7 +19822,12 @@
       </c>
       <c r="CX39" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="CY39" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -19674,12 +19869,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -19694,7 +19889,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -19819,7 +20014,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>2026-01-15 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
@@ -19845,12 +20040,12 @@
       <c r="AP40" t="inlineStr"/>
       <c r="AQ40" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AR40" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr">
@@ -19923,7 +20118,7 @@
       </c>
       <c r="BI40" t="inlineStr">
         <is>
-          <t>2260026082.286561</t>
+          <t>3608269246.254</t>
         </is>
       </c>
       <c r="BJ40" t="inlineStr">
@@ -19949,12 +20144,12 @@
       </c>
       <c r="BO40" t="inlineStr">
         <is>
-          <t>372592895.4598678</t>
+          <t>372592895.4598611</t>
         </is>
       </c>
       <c r="BP40" t="inlineStr">
         <is>
-          <t>216676253.9753027</t>
+          <t>216676253.9753013</t>
         </is>
       </c>
       <c r="BQ40" t="inlineStr">
@@ -20039,7 +20234,7 @@
       </c>
       <c r="CG40" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="CH40" t="inlineStr">
@@ -20049,7 +20244,7 @@
       </c>
       <c r="CI40" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="CJ40" t="inlineStr">
@@ -20064,12 +20259,12 @@
       </c>
       <c r="CL40" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM40" t="inlineStr">
         <is>
-          <t>194155</t>
+          <t>196532</t>
         </is>
       </c>
       <c r="CN40" t="inlineStr">
@@ -20124,7 +20319,12 @@
       </c>
       <c r="CX40" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="CY40" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -20166,12 +20366,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-6.73</t>
+          <t>-5.44</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -20186,7 +20386,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -20311,7 +20511,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>2026-01-15 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL41" t="inlineStr">
@@ -20337,12 +20537,12 @@
       <c r="AP41" t="inlineStr"/>
       <c r="AQ41" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AR41" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr">
@@ -20415,7 +20615,7 @@
       </c>
       <c r="BI41" t="inlineStr">
         <is>
-          <t>2260026082.286561</t>
+          <t>3608269246.254</t>
         </is>
       </c>
       <c r="BJ41" t="inlineStr">
@@ -20441,12 +20641,12 @@
       </c>
       <c r="BO41" t="inlineStr">
         <is>
-          <t>400941375.7297887</t>
+          <t>400941375.7297811</t>
         </is>
       </c>
       <c r="BP41" t="inlineStr">
         <is>
-          <t>459058866.4216776</t>
+          <t>459058866.4216757</t>
         </is>
       </c>
       <c r="BQ41" t="inlineStr">
@@ -20531,7 +20731,7 @@
       </c>
       <c r="CG41" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="CH41" t="inlineStr">
@@ -20541,7 +20741,7 @@
       </c>
       <c r="CI41" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="CJ41" t="inlineStr">
@@ -20556,12 +20756,12 @@
       </c>
       <c r="CL41" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM41" t="inlineStr">
         <is>
-          <t>194155</t>
+          <t>196532</t>
         </is>
       </c>
       <c r="CN41" t="inlineStr">
@@ -20616,7 +20816,12 @@
       </c>
       <c r="CX41" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="CY41" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -20658,12 +20863,12 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-9.42</t>
+          <t>-8.1</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -20678,7 +20883,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -20803,7 +21008,7 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>2026-01-15 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
@@ -20829,12 +21034,12 @@
       <c r="AP42" t="inlineStr"/>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
@@ -20907,7 +21112,7 @@
       </c>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>2260026082.286561</t>
+          <t>3608269246.254</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr">
@@ -20933,12 +21138,12 @@
       </c>
       <c r="BO42" t="inlineStr">
         <is>
-          <t>390374559.2403544</t>
+          <t>390374559.2403457</t>
         </is>
       </c>
       <c r="BP42" t="inlineStr">
         <is>
-          <t>715680329.4371533</t>
+          <t>715680329.437151</t>
         </is>
       </c>
       <c r="BQ42" t="inlineStr">
@@ -21023,7 +21228,7 @@
       </c>
       <c r="CG42" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="CH42" t="inlineStr">
@@ -21033,7 +21238,7 @@
       </c>
       <c r="CI42" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="CJ42" t="inlineStr">
@@ -21048,12 +21253,12 @@
       </c>
       <c r="CL42" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM42" t="inlineStr">
         <is>
-          <t>194155</t>
+          <t>196532</t>
         </is>
       </c>
       <c r="CN42" t="inlineStr">
@@ -21108,7 +21313,12 @@
       </c>
       <c r="CX42" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="CY42" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -21150,12 +21360,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-9.3</t>
+          <t>-7.98</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -21170,7 +21380,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -21295,7 +21505,7 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>2026-01-15 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
@@ -21321,12 +21531,12 @@
       <c r="AP43" t="inlineStr"/>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
@@ -21399,7 +21609,7 @@
       </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>2260026082.286561</t>
+          <t>3608269246.254</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr">
@@ -21425,12 +21635,12 @@
       </c>
       <c r="BO43" t="inlineStr">
         <is>
-          <t>331228055.5682092</t>
+          <t>331228055.5681993</t>
         </is>
       </c>
       <c r="BP43" t="inlineStr">
         <is>
-          <t>628465198.2650776</t>
+          <t>628465198.2650752</t>
         </is>
       </c>
       <c r="BQ43" t="inlineStr">
@@ -21505,7 +21715,7 @@
       </c>
       <c r="CE43" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF43" t="inlineStr">
@@ -21515,7 +21725,7 @@
       </c>
       <c r="CG43" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="CH43" t="inlineStr">
@@ -21525,7 +21735,7 @@
       </c>
       <c r="CI43" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="CJ43" t="inlineStr">
@@ -21540,12 +21750,12 @@
       </c>
       <c r="CL43" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM43" t="inlineStr">
         <is>
-          <t>194155</t>
+          <t>196532</t>
         </is>
       </c>
       <c r="CN43" t="inlineStr">
@@ -21600,7 +21810,12 @@
       </c>
       <c r="CX43" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="CY43" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -21642,12 +21857,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -21662,7 +21877,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -21787,7 +22002,7 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>2026-01-15 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
@@ -21813,12 +22028,12 @@
       <c r="AP44" t="inlineStr"/>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
@@ -21891,7 +22106,7 @@
       </c>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>2260026082.286561</t>
+          <t>3608269246.254</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr">
@@ -21917,12 +22132,12 @@
       </c>
       <c r="BO44" t="inlineStr">
         <is>
-          <t>277184938.7142331</t>
+          <t>277184938.7142218</t>
         </is>
       </c>
       <c r="BP44" t="inlineStr">
         <is>
-          <t>566503031.3312163</t>
+          <t>566503031.3312135</t>
         </is>
       </c>
       <c r="BQ44" t="inlineStr">
@@ -22007,7 +22222,7 @@
       </c>
       <c r="CG44" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="CH44" t="inlineStr">
@@ -22017,7 +22232,7 @@
       </c>
       <c r="CI44" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>35.96</t>
         </is>
       </c>
       <c r="CJ44" t="inlineStr">
@@ -22032,12 +22247,12 @@
       </c>
       <c r="CL44" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM44" t="inlineStr">
         <is>
-          <t>194155</t>
+          <t>196532</t>
         </is>
       </c>
       <c r="CN44" t="inlineStr">
@@ -22092,29 +22307,34 @@
       </c>
       <c r="CX44" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="CY44" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1504</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>53115.543</t>
+          <t>2796.233</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -22124,7 +22344,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>221.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -22134,17 +22354,17 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-8.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>68.10</t>
+          <t>-24.55</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -22154,37 +22374,37 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2025-09-24 00:00:00</t>
+          <t>2026-01-16 00:00:00</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2025-10-14 00:00:00</t>
+          <t>2026-02-03 00:00:00</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2025-09-09 00:00:00</t>
+          <t>2025-09-04 00:00:00</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2025-09-19 00:00:00</t>
+          <t>2025-09-17 00:00:00</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>101.5</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -22194,12 +22414,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>193.0</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>183.0</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -22209,22 +22429,22 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>7.65</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025/05/21</t>
+          <t>2025/09/01</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>191.0</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -22234,47 +22454,47 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>2025/11/26</t>
+          <t>2025/10/13</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>177.0</t>
         </is>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2025/06/30</t>
+          <t>2025/08/14</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>176.5</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>2026/01/30</t>
+          <t>2026/02/03</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>2025/10/14</t>
+          <t>2026/01/06</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>169.5</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -22284,17 +22504,17 @@
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -22305,121 +22525,121 @@
       <c r="AP45" t="inlineStr"/>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>18.33</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>7.21</t>
         </is>
       </c>
       <c r="AU45" t="n">
-        <v>0.48</v>
+        <v>-1.51</v>
       </c>
       <c r="AV45" t="n">
-        <v>3.42</v>
+        <v>6.6</v>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>88.38000000000001</t>
+          <t>224.9</t>
         </is>
       </c>
       <c r="AZ45" t="n">
-        <v>85.45999999999999</v>
+        <v>210.98</v>
       </c>
       <c r="BA45" t="n">
-        <v>88.75</v>
+        <v>185.85</v>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>96.69</t>
+          <t>182.54</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>81.24</t>
+          <t>-7.18</t>
         </is>
       </c>
       <c r="BD45" t="n">
-        <v>-0.22</v>
+        <v>12.67</v>
       </c>
       <c r="BE45" t="n">
-        <v>-1.19</v>
+        <v>13.65</v>
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr">
         <is>
-          <t>-112.02</t>
+          <t>-2.34</t>
         </is>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2025/12/11</t>
+          <t>2026/01/07</t>
         </is>
       </c>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>2260026082.286561</t>
+          <t>1154714843.898406</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr">
         <is>
-          <t>4736361527.0</t>
+          <t>615501795.0</t>
         </is>
       </c>
       <c r="BK45" t="n">
-        <v>5454464369.4</v>
+        <v>1802497222.2</v>
       </c>
       <c r="BL45" t="inlineStr">
         <is>
-          <t>3244854301.4</t>
+          <t>2388964892.6</t>
         </is>
       </c>
       <c r="BM45" t="n">
-        <v>2626366381.86</v>
+        <v>1002635113.02</v>
       </c>
       <c r="BN45" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-586467670</t>
         </is>
       </c>
       <c r="BO45" t="inlineStr">
         <is>
-          <t>224581649.1475089</t>
+          <t>219009022.3363868</t>
         </is>
       </c>
       <c r="BP45" t="inlineStr">
         <is>
-          <t>670296675.9852996</t>
+          <t>-111895808.3624005</t>
         </is>
       </c>
       <c r="BQ45" t="inlineStr">
         <is>
-          <t>4736361527.0</t>
+          <t>615501795.0</t>
         </is>
       </c>
       <c r="BR45" t="inlineStr">
@@ -22429,27 +22649,27 @@
       </c>
       <c r="BS45" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>198.0</t>
         </is>
       </c>
       <c r="BT45" t="inlineStr">
         <is>
-          <t>2025/08/11</t>
+          <t>2026/01/14</t>
         </is>
       </c>
       <c r="BU45" t="inlineStr">
         <is>
-          <t>60.58</t>
+          <t>11.87</t>
         </is>
       </c>
       <c r="BV45" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="BW45" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="BX45" t="inlineStr">
@@ -22464,82 +22684,82 @@
       </c>
       <c r="BZ45" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="CA45" t="inlineStr">
         <is>
-          <t>20.96595910135787</t>
+          <t>37.43284124074289</t>
         </is>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>15.63698930879905</t>
+          <t>17.70634106044967</t>
         </is>
       </c>
       <c r="CC45" t="inlineStr">
         <is>
-          <t>6.485882553210391</t>
+          <t>6.007181231999267</t>
         </is>
       </c>
       <c r="CD45" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE45" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="CF45" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="CG45" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CH45" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>16.01</t>
         </is>
       </c>
       <c r="CI45" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="CJ45" t="inlineStr">
         <is>
-          <t>24.44%</t>
+          <t>19.80%</t>
         </is>
       </c>
       <c r="CK45" t="inlineStr">
         <is>
-          <t>11.24%</t>
+          <t>9.44%</t>
         </is>
       </c>
       <c r="CL45" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM45" t="inlineStr">
         <is>
-          <t>194155</t>
+          <t>115395</t>
         </is>
       </c>
       <c r="CN45" t="inlineStr">
         <is>
-          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
+          <t>配電69.99%、汽車零件16.96%、自動化設備及零件9.91%、其他類3.14% (2024年)</t>
         </is>
       </c>
       <c r="CO45" t="inlineStr">
         <is>
-          <t>東元-電機機械-上市</t>
+          <t>士電-電機機械-上市</t>
         </is>
       </c>
       <c r="CP45" t="inlineStr">
@@ -22549,42 +22769,47 @@
       </c>
       <c r="CQ45" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CR45" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>223.5</t>
         </is>
       </c>
       <c r="CS45" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CT45" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>221.5</t>
         </is>
       </c>
       <c r="CU45" t="inlineStr">
         <is>
-          <t>37.41</t>
+          <t>69.75</t>
         </is>
       </c>
       <c r="CV45" t="inlineStr">
         <is>
-          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
+          <t>** 電腦及週邊設備 - 安全監控系統** 電機機械 - 輸送機械及零配件、車用機械傳動設備及零配件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 汽車 - 其他** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 電力系統</t>
         </is>
       </c>
       <c r="CW45" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="CX45" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY45" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -22626,12 +22851,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -22646,7 +22871,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -22771,7 +22996,7 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-15 00:00:00</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
@@ -22797,12 +23022,12 @@
       <c r="AP46" t="inlineStr"/>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
@@ -22860,12 +23085,12 @@
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr">
         <is>
-          <t>-61.75</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="BH46" t="inlineStr">
@@ -22875,7 +23100,7 @@
       </c>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>2380718892.029586</t>
+          <t>1154714843.898406</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr">
@@ -22901,7 +23126,7 @@
       </c>
       <c r="BO46" t="inlineStr">
         <is>
-          <t>279173537.0088947</t>
+          <t>279173537.0088935</t>
         </is>
       </c>
       <c r="BP46" t="inlineStr">
@@ -22991,7 +23216,7 @@
       </c>
       <c r="CG46" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CH46" t="inlineStr">
@@ -23001,7 +23226,7 @@
       </c>
       <c r="CI46" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="CJ46" t="inlineStr">
@@ -23016,12 +23241,12 @@
       </c>
       <c r="CL46" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM46" t="inlineStr">
         <is>
-          <t>112790</t>
+          <t>115395</t>
         </is>
       </c>
       <c r="CN46" t="inlineStr">
@@ -23036,7 +23261,7 @@
       </c>
       <c r="CP46" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="CQ46" t="inlineStr">
@@ -23076,7 +23301,12 @@
       </c>
       <c r="CX46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY46" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -23118,12 +23348,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -23138,7 +23368,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -23263,7 +23493,7 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-15 00:00:00</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
@@ -23289,12 +23519,12 @@
       <c r="AP47" t="inlineStr"/>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
@@ -23352,12 +23582,12 @@
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="BG47" t="inlineStr">
         <is>
-          <t>-61.53</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH47" t="inlineStr">
@@ -23367,7 +23597,7 @@
       </c>
       <c r="BI47" t="inlineStr">
         <is>
-          <t>2380718892.029586</t>
+          <t>1154714843.898406</t>
         </is>
       </c>
       <c r="BJ47" t="inlineStr">
@@ -23393,7 +23623,7 @@
       </c>
       <c r="BO47" t="inlineStr">
         <is>
-          <t>328628749.6381958</t>
+          <t>328628749.6381944</t>
         </is>
       </c>
       <c r="BP47" t="inlineStr">
@@ -23483,7 +23713,7 @@
       </c>
       <c r="CG47" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CH47" t="inlineStr">
@@ -23493,7 +23723,7 @@
       </c>
       <c r="CI47" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="CJ47" t="inlineStr">
@@ -23508,12 +23738,12 @@
       </c>
       <c r="CL47" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM47" t="inlineStr">
         <is>
-          <t>112790</t>
+          <t>115395</t>
         </is>
       </c>
       <c r="CN47" t="inlineStr">
@@ -23528,7 +23758,7 @@
       </c>
       <c r="CP47" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="CQ47" t="inlineStr">
@@ -23568,7 +23798,12 @@
       </c>
       <c r="CX47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY47" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -23610,12 +23845,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-5.77</t>
+          <t>-3.39</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -23630,7 +23865,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -23755,7 +23990,7 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-15 00:00:00</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
@@ -23781,12 +24016,12 @@
       <c r="AP48" t="inlineStr"/>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
@@ -23844,12 +24079,12 @@
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="BG48" t="inlineStr">
         <is>
-          <t>-62.24</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="BH48" t="inlineStr">
@@ -23859,7 +24094,7 @@
       </c>
       <c r="BI48" t="inlineStr">
         <is>
-          <t>2380718892.029586</t>
+          <t>1154714843.898406</t>
         </is>
       </c>
       <c r="BJ48" t="inlineStr">
@@ -23885,7 +24120,7 @@
       </c>
       <c r="BO48" t="inlineStr">
         <is>
-          <t>365428090.7140074</t>
+          <t>365428090.7140058</t>
         </is>
       </c>
       <c r="BP48" t="inlineStr">
@@ -23975,7 +24210,7 @@
       </c>
       <c r="CG48" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CH48" t="inlineStr">
@@ -23985,7 +24220,7 @@
       </c>
       <c r="CI48" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="CJ48" t="inlineStr">
@@ -24000,12 +24235,12 @@
       </c>
       <c r="CL48" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM48" t="inlineStr">
         <is>
-          <t>112790</t>
+          <t>115395</t>
         </is>
       </c>
       <c r="CN48" t="inlineStr">
@@ -24020,7 +24255,7 @@
       </c>
       <c r="CP48" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="CQ48" t="inlineStr">
@@ -24060,7 +24295,12 @@
       </c>
       <c r="CX48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY48" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -24102,12 +24342,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-11.55</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -24122,7 +24362,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -24247,7 +24487,7 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-15 00:00:00</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
@@ -24273,12 +24513,12 @@
       <c r="AP49" t="inlineStr"/>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
@@ -24336,12 +24576,12 @@
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr">
         <is>
-          <t>-64.30</t>
+          <t>-7.20</t>
         </is>
       </c>
       <c r="BH49" t="inlineStr">
@@ -24351,7 +24591,7 @@
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>2380718892.029586</t>
+          <t>1154714843.898406</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr">
@@ -24377,7 +24617,7 @@
       </c>
       <c r="BO49" t="inlineStr">
         <is>
-          <t>385321617.8216643</t>
+          <t>385321617.8216624</t>
         </is>
       </c>
       <c r="BP49" t="inlineStr">
@@ -24467,7 +24707,7 @@
       </c>
       <c r="CG49" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CH49" t="inlineStr">
@@ -24477,7 +24717,7 @@
       </c>
       <c r="CI49" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="CJ49" t="inlineStr">
@@ -24492,12 +24732,12 @@
       </c>
       <c r="CL49" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM49" t="inlineStr">
         <is>
-          <t>112790</t>
+          <t>115395</t>
         </is>
       </c>
       <c r="CN49" t="inlineStr">
@@ -24512,7 +24752,7 @@
       </c>
       <c r="CP49" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="CQ49" t="inlineStr">
@@ -24552,7 +24792,12 @@
       </c>
       <c r="CX49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY49" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -24594,12 +24839,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-13.63</t>
+          <t>-11.06</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -24614,7 +24859,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -24739,7 +24984,7 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-15 00:00:00</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
@@ -24765,12 +25010,12 @@
       <c r="AP50" t="inlineStr"/>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
@@ -24828,12 +25073,12 @@
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr">
         <is>
-          <t>-67.27</t>
+          <t>-14.93</t>
         </is>
       </c>
       <c r="BH50" t="inlineStr">
@@ -24843,7 +25088,7 @@
       </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>2380718892.029586</t>
+          <t>1154714843.898406</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr">
@@ -24869,12 +25114,12 @@
       </c>
       <c r="BO50" t="inlineStr">
         <is>
-          <t>382172730.6670474</t>
+          <t>382172730.6670452</t>
         </is>
       </c>
       <c r="BP50" t="inlineStr">
         <is>
-          <t>331600431.2732882</t>
+          <t>331600431.2732878</t>
         </is>
       </c>
       <c r="BQ50" t="inlineStr">
@@ -24959,7 +25204,7 @@
       </c>
       <c r="CG50" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CH50" t="inlineStr">
@@ -24969,7 +25214,7 @@
       </c>
       <c r="CI50" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="CJ50" t="inlineStr">
@@ -24984,12 +25229,12 @@
       </c>
       <c r="CL50" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM50" t="inlineStr">
         <is>
-          <t>112790</t>
+          <t>115395</t>
         </is>
       </c>
       <c r="CN50" t="inlineStr">
@@ -25004,7 +25249,7 @@
       </c>
       <c r="CP50" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="CQ50" t="inlineStr">
@@ -25044,7 +25289,12 @@
       </c>
       <c r="CX50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY50" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -25086,12 +25336,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -25106,7 +25356,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -25231,7 +25481,7 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-15 00:00:00</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
@@ -25257,12 +25507,12 @@
       <c r="AP51" t="inlineStr"/>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
@@ -25320,12 +25570,12 @@
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="BG51" t="inlineStr">
         <is>
-          <t>-70.46</t>
+          <t>-23.21</t>
         </is>
       </c>
       <c r="BH51" t="inlineStr">
@@ -25335,7 +25585,7 @@
       </c>
       <c r="BI51" t="inlineStr">
         <is>
-          <t>2380718892.029586</t>
+          <t>1154714843.898406</t>
         </is>
       </c>
       <c r="BJ51" t="inlineStr">
@@ -25361,12 +25611,12 @@
       </c>
       <c r="BO51" t="inlineStr">
         <is>
-          <t>391367694.1931854</t>
+          <t>391367694.1931829</t>
         </is>
       </c>
       <c r="BP51" t="inlineStr">
         <is>
-          <t>272779798.3724298</t>
+          <t>272779798.3724289</t>
         </is>
       </c>
       <c r="BQ51" t="inlineStr">
@@ -25451,7 +25701,7 @@
       </c>
       <c r="CG51" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CH51" t="inlineStr">
@@ -25461,7 +25711,7 @@
       </c>
       <c r="CI51" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="CJ51" t="inlineStr">
@@ -25476,12 +25726,12 @@
       </c>
       <c r="CL51" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM51" t="inlineStr">
         <is>
-          <t>112790</t>
+          <t>115395</t>
         </is>
       </c>
       <c r="CN51" t="inlineStr">
@@ -25496,7 +25746,7 @@
       </c>
       <c r="CP51" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="CQ51" t="inlineStr">
@@ -25536,7 +25786,12 @@
       </c>
       <c r="CX51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY51" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -25578,12 +25833,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-5.31</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -25598,7 +25853,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -25723,7 +25978,7 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-15 00:00:00</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
@@ -25749,12 +26004,12 @@
       <c r="AP52" t="inlineStr"/>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
@@ -25812,12 +26067,12 @@
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="BG52" t="inlineStr">
         <is>
-          <t>-73.27</t>
+          <t>-30.54</t>
         </is>
       </c>
       <c r="BH52" t="inlineStr">
@@ -25827,7 +26082,7 @@
       </c>
       <c r="BI52" t="inlineStr">
         <is>
-          <t>2380718892.029586</t>
+          <t>1154714843.898406</t>
         </is>
       </c>
       <c r="BJ52" t="inlineStr">
@@ -25853,12 +26108,12 @@
       </c>
       <c r="BO52" t="inlineStr">
         <is>
-          <t>412929129.7969592</t>
+          <t>412929129.7969564</t>
         </is>
       </c>
       <c r="BP52" t="inlineStr">
         <is>
-          <t>463395487.0721879</t>
+          <t>463395487.0721869</t>
         </is>
       </c>
       <c r="BQ52" t="inlineStr">
@@ -25943,7 +26198,7 @@
       </c>
       <c r="CG52" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CH52" t="inlineStr">
@@ -25953,7 +26208,7 @@
       </c>
       <c r="CI52" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="CJ52" t="inlineStr">
@@ -25968,12 +26223,12 @@
       </c>
       <c r="CL52" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM52" t="inlineStr">
         <is>
-          <t>112790</t>
+          <t>115395</t>
         </is>
       </c>
       <c r="CN52" t="inlineStr">
@@ -25988,7 +26243,7 @@
       </c>
       <c r="CP52" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="CQ52" t="inlineStr">
@@ -26028,7 +26283,12 @@
       </c>
       <c r="CX52" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CY52" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -26070,12 +26330,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -26090,7 +26350,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -26215,7 +26475,7 @@
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-15 00:00:00</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
@@ -26241,12 +26501,12 @@
       <c r="AP53" t="inlineStr"/>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
@@ -26304,12 +26564,12 @@
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="BG53" t="inlineStr">
         <is>
-          <t>-76.71</t>
+          <t>-39.46</t>
         </is>
       </c>
       <c r="BH53" t="inlineStr">
@@ -26319,7 +26579,7 @@
       </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>2380718892.029586</t>
+          <t>1154714843.898406</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr">
@@ -26345,12 +26605,12 @@
       </c>
       <c r="BO53" t="inlineStr">
         <is>
-          <t>403753428.4741904</t>
+          <t>403753428.4741871</t>
         </is>
       </c>
       <c r="BP53" t="inlineStr">
         <is>
-          <t>652166994.3906927</t>
+          <t>652166994.3906918</t>
         </is>
       </c>
       <c r="BQ53" t="inlineStr">
@@ -26425,7 +26685,7 @@
       </c>
       <c r="CE53" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF53" t="inlineStr">
@@ -26435,7 +26695,7 @@
       </c>
       <c r="CG53" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CH53" t="inlineStr">
@@ -26445,7 +26705,7 @@
       </c>
       <c r="CI53" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="CJ53" t="inlineStr">
@@ -26460,12 +26720,12 @@
       </c>
       <c r="CL53" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM53" t="inlineStr">
         <is>
-          <t>112790</t>
+          <t>115395</t>
         </is>
       </c>
       <c r="CN53" t="inlineStr">
@@ -26480,7 +26740,7 @@
       </c>
       <c r="CP53" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="CQ53" t="inlineStr">
@@ -26520,7 +26780,12 @@
       </c>
       <c r="CX53" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="CY53" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -26562,12 +26827,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-9.47</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -26582,7 +26847,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -26707,7 +26972,7 @@
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-15 00:00:00</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
@@ -26733,12 +26998,12 @@
       <c r="AP54" t="inlineStr"/>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
@@ -26796,12 +27061,12 @@
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="BG54" t="inlineStr">
         <is>
-          <t>-80.46</t>
+          <t>-49.21</t>
         </is>
       </c>
       <c r="BH54" t="inlineStr">
@@ -26811,7 +27076,7 @@
       </c>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>2380718892.029586</t>
+          <t>1154714843.898406</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr">
@@ -26837,12 +27102,12 @@
       </c>
       <c r="BO54" t="inlineStr">
         <is>
-          <t>358587325.5802809</t>
+          <t>358587325.5802772</t>
         </is>
       </c>
       <c r="BP54" t="inlineStr">
         <is>
-          <t>685545884.6174598</t>
+          <t>685545884.6174588</t>
         </is>
       </c>
       <c r="BQ54" t="inlineStr">
@@ -26917,7 +27182,7 @@
       </c>
       <c r="CE54" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF54" t="inlineStr">
@@ -26927,7 +27192,7 @@
       </c>
       <c r="CG54" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CH54" t="inlineStr">
@@ -26937,7 +27202,7 @@
       </c>
       <c r="CI54" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="CJ54" t="inlineStr">
@@ -26952,12 +27217,12 @@
       </c>
       <c r="CL54" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM54" t="inlineStr">
         <is>
-          <t>112790</t>
+          <t>115395</t>
         </is>
       </c>
       <c r="CN54" t="inlineStr">
@@ -26972,7 +27237,7 @@
       </c>
       <c r="CP54" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="CQ54" t="inlineStr">
@@ -27012,7 +27277,12 @@
       </c>
       <c r="CX54" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="CY54" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -27054,12 +27324,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -27074,7 +27344,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -27199,7 +27469,7 @@
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>2026-01-19 00:00:00</t>
+          <t>2026-01-15 00:00:00</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
@@ -27225,12 +27495,12 @@
       <c r="AP55" t="inlineStr"/>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
@@ -27288,12 +27558,12 @@
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>13.98</t>
         </is>
       </c>
       <c r="BG55" t="inlineStr">
         <is>
-          <t>-84.46</t>
+          <t>-59.61</t>
         </is>
       </c>
       <c r="BH55" t="inlineStr">
@@ -27303,7 +27573,7 @@
       </c>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>2380718892.029586</t>
+          <t>1154714843.898406</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr">
@@ -27329,12 +27599,12 @@
       </c>
       <c r="BO55" t="inlineStr">
         <is>
-          <t>299140314.8462484</t>
+          <t>299140314.8462442</t>
         </is>
       </c>
       <c r="BP55" t="inlineStr">
         <is>
-          <t>573042392.8122184</t>
+          <t>573042392.8122175</t>
         </is>
       </c>
       <c r="BQ55" t="inlineStr">
@@ -27419,7 +27689,7 @@
       </c>
       <c r="CG55" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="CH55" t="inlineStr">
@@ -27429,7 +27699,7 @@
       </c>
       <c r="CI55" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>35.16</t>
         </is>
       </c>
       <c r="CJ55" t="inlineStr">
@@ -27444,12 +27714,12 @@
       </c>
       <c r="CL55" t="inlineStr">
         <is>
-          <t>252.82</t>
+          <t>252.55</t>
         </is>
       </c>
       <c r="CM55" t="inlineStr">
         <is>
-          <t>112790</t>
+          <t>115395</t>
         </is>
       </c>
       <c r="CN55" t="inlineStr">
@@ -27464,7 +27734,7 @@
       </c>
       <c r="CP55" t="inlineStr">
         <is>
-          <t>電機機械平上市</t>
+          <t>電機機械右上上市</t>
         </is>
       </c>
       <c r="CQ55" t="inlineStr">
@@ -27504,499 +27774,12 @@
       </c>
       <c r="CX55" t="inlineStr">
         <is>
-          <t>3.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>【b1】</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>5.35</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>15191.806</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>218.0</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>-1.79</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>74.64</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>2026-01-16 00:00:00</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>2026-02-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>2025-09-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>2025-09-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>197.0</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>216.5</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>197.0</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>193.0</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>183.0</t>
-        </is>
-      </c>
-      <c r="V56" t="inlineStr">
-        <is>
-          <t>10.66</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>0.69</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>7.65</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>2025/09/01</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>191.0</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>2025/10/13</t>
-        </is>
-      </c>
-      <c r="AD56" t="inlineStr">
-        <is>
-          <t>177.0</t>
-        </is>
-      </c>
-      <c r="AE56" t="inlineStr">
-        <is>
-          <t>2025/08/14</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>176.5</t>
-        </is>
-      </c>
-      <c r="AG56" t="inlineStr">
-        <is>
-          <t>2026/02/03</t>
-        </is>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>216.5</t>
-        </is>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>2026/01/06</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>169.5</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>2026-01-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL56" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>34.89</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>5.26</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP56" t="inlineStr"/>
-      <c r="AQ56" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>4964</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AT56" t="inlineStr">
-        <is>
-          <t>98.83</t>
-        </is>
-      </c>
-      <c r="AU56" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>12.91</v>
-      </c>
-      <c r="AW56" t="inlineStr">
-        <is>
-          <t>4.09</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>-1.70</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>203.4</t>
-        </is>
-      </c>
-      <c r="AZ56" t="n">
-        <v>180.15</v>
-      </c>
-      <c r="BA56" t="n">
-        <v>173.07</v>
-      </c>
-      <c r="BB56" t="inlineStr">
-        <is>
-          <t>176.07</t>
-        </is>
-      </c>
-      <c r="BC56" t="inlineStr">
-        <is>
-          <t>102.37</t>
-        </is>
-      </c>
-      <c r="BD56" t="n">
-        <v>9.06</v>
-      </c>
-      <c r="BE56" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="BF56" t="inlineStr">
-        <is>
-          <t>36.33</t>
-        </is>
-      </c>
-      <c r="BG56" t="inlineStr">
-        <is>
-          <t>-87.68</t>
-        </is>
-      </c>
-      <c r="BH56" t="inlineStr">
-        <is>
-          <t>2026/01/07</t>
-        </is>
-      </c>
-      <c r="BI56" t="inlineStr">
-        <is>
-          <t>2380718892.029586</t>
-        </is>
-      </c>
-      <c r="BJ56" t="inlineStr">
-        <is>
-          <t>3252837191.0</t>
-        </is>
-      </c>
-      <c r="BK56" t="n">
-        <v>2979333840.6</v>
-      </c>
-      <c r="BL56" t="inlineStr">
-        <is>
-          <t>1705942607.9</t>
-        </is>
-      </c>
-      <c r="BM56" t="n">
-        <v>546987858.54</v>
-      </c>
-      <c r="BN56" t="inlineStr">
-        <is>
-          <t>1273391232</t>
-        </is>
-      </c>
-      <c r="BO56" t="inlineStr">
-        <is>
-          <t>249339937.0342538</t>
-        </is>
-      </c>
-      <c r="BP56" t="inlineStr">
-        <is>
-          <t>549792709.9185803</t>
-        </is>
-      </c>
-      <c r="BQ56" t="inlineStr">
-        <is>
-          <t>3252837191.0</t>
-        </is>
-      </c>
-      <c r="BR56" t="inlineStr">
-        <is>
-          <t>2026-02-03</t>
-        </is>
-      </c>
-      <c r="BS56" t="inlineStr">
-        <is>
-          <t>198.0</t>
-        </is>
-      </c>
-      <c r="BT56" t="inlineStr">
-        <is>
-          <t>2026/01/14</t>
-        </is>
-      </c>
-      <c r="BU56" t="inlineStr">
-        <is>
-          <t>10.10</t>
-        </is>
-      </c>
-      <c r="BV56" t="inlineStr">
-        <is>
-          <t>士電</t>
-        </is>
-      </c>
-      <c r="BW56" t="inlineStr">
-        <is>
-          <t>士電</t>
-        </is>
-      </c>
-      <c r="BX56" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BY56" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ56" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="CA56" t="inlineStr">
-        <is>
-          <t>37.43284124074289</t>
-        </is>
-      </c>
-      <c r="CB56" t="inlineStr">
-        <is>
-          <t>17.70634106044967</t>
-        </is>
-      </c>
-      <c r="CC56" t="inlineStr">
-        <is>
-          <t>6.007181231999267</t>
-        </is>
-      </c>
-      <c r="CD56" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE56" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF56" t="inlineStr">
-        <is>
-          <t>3.13</t>
-        </is>
-      </c>
-      <c r="CG56" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="CH56" t="inlineStr">
-        <is>
-          <t>16.01</t>
-        </is>
-      </c>
-      <c r="CI56" t="inlineStr">
-        <is>
-          <t>34.37</t>
-        </is>
-      </c>
-      <c r="CJ56" t="inlineStr">
-        <is>
-          <t>19.80%</t>
-        </is>
-      </c>
-      <c r="CK56" t="inlineStr">
-        <is>
-          <t>9.44%</t>
-        </is>
-      </c>
-      <c r="CL56" t="inlineStr">
-        <is>
-          <t>252.82</t>
-        </is>
-      </c>
-      <c r="CM56" t="inlineStr">
-        <is>
-          <t>112790</t>
-        </is>
-      </c>
-      <c r="CN56" t="inlineStr">
-        <is>
-          <t>配電69.99%、汽車零件16.96%、自動化設備及零件9.91%、其他類3.14% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO56" t="inlineStr">
-        <is>
-          <t>士電-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CP56" t="inlineStr">
-        <is>
-          <t>電機機械平上市</t>
-        </is>
-      </c>
-      <c r="CQ56" t="inlineStr">
-        <is>
-          <t>205.5</t>
-        </is>
-      </c>
-      <c r="CR56" t="inlineStr">
-        <is>
-          <t>221.5</t>
-        </is>
-      </c>
-      <c r="CS56" t="inlineStr">
-        <is>
-          <t>204.0</t>
-        </is>
-      </c>
-      <c r="CT56" t="inlineStr">
-        <is>
-          <t>218.0</t>
-        </is>
-      </c>
-      <c r="CU56" t="inlineStr">
-        <is>
-          <t>69.75</t>
-        </is>
-      </c>
-      <c r="CV56" t="inlineStr">
-        <is>
-          <t>** 電腦及週邊設備 - 安全監控系統** 電機機械 - 輸送機械及零配件、車用機械傳動設備及零配件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 汽車 - 其他** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 電力系統</t>
-        </is>
-      </c>
-      <c r="CW56" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CX56" t="inlineStr">
-        <is>
-          <t>3.0</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="CY55" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
     </row>
